--- a/artfynd/A 37042-2026 artfynd.xlsx
+++ b/artfynd/A 37042-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1240,48 +1240,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136880270</v>
+        <v>136933792</v>
       </c>
       <c r="B7" t="n">
-        <v>78879</v>
+        <v>79476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Venetvaara, Lu lm</t>
+          <t>Iso Venetvaara, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>772986</v>
+        <v>773149</v>
       </c>
       <c r="R7" t="n">
-        <v>7411352</v>
+        <v>7411741</v>
       </c>
       <c r="S7" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,27 +1335,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Lindmark</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Lindmark</t>
+          <t>Elin Kannerby, Ida Jansson, Severin Suess, Hannes Weiss, Anders Lindmark, Ignacio Gomez-Lobo</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136880270</t>
+          <t>https://artportalen.se/Sighting/136933792</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136880271</v>
+        <v>136880270</v>
       </c>
       <c r="B8" t="n">
-        <v>80066</v>
+        <v>78879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,13 +1387,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>772982</v>
+        <v>772986</v>
       </c>
       <c r="R8" t="n">
-        <v>7411363</v>
+        <v>7411352</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1458,16 +1458,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136880271</t>
+          <t>https://artportalen.se/Sighting/136880270</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136880269</v>
+        <v>136933795</v>
       </c>
       <c r="B9" t="n">
-        <v>79499</v>
+        <v>78879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,37 +1475,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>260591</v>
+        <v>6437</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Venetvaara, Lu lm</t>
+          <t>Iso Venetvaara, Lu lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>772921</v>
+        <v>772851</v>
       </c>
       <c r="R9" t="n">
-        <v>7411389</v>
+        <v>7411541</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,16 +1559,586 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Lindmark</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Lindmark</t>
+          <t>Elin Kannerby, Ida Jansson, Severin Suess, Hannes Weiss, Anders Lindmark, Ignacio Gomez-Lobo</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136933795</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136933796</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80596</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Iso Venetvaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>772891</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7411428</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Ida Jansson, Severin Suess, Hannes Weiss, Anders Lindmark, Ignacio Gomez-Lobo</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136933796</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136933794</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78480</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Iso Venetvaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>772851</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7411541</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Ida Jansson, Severin Suess, Hannes Weiss, Anders Lindmark, Ignacio Gomez-Lobo</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136933794</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136933793</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Iso Venetvaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>773002</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7411665</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Barkfläkning från födosök</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Ida Jansson, Severin Suess, Hannes Weiss, Anders Lindmark, Ignacio Gomez-Lobo</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136933793</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136880271</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80066</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Venetvaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>772982</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7411363</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anders Lindmark</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anders Lindmark</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136880271</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136880269</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Venetvaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>772921</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7411389</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anders Lindmark</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anders Lindmark</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136880269</t>
         </is>
@@ -1584,6 +2154,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37042-2026 artfynd.xlsx
+++ b/artfynd/A 37042-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136880268</v>
       </c>
       <c r="B2" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136877193</v>
       </c>
       <c r="B3" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136880272</v>
       </c>
       <c r="B4" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136880266</v>
       </c>
       <c r="B5" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136880267</v>
       </c>
       <c r="B6" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136933792</v>
       </c>
       <c r="B7" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136880270</v>
       </c>
       <c r="B8" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136933795</v>
       </c>
       <c r="B9" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136933796</v>
       </c>
       <c r="B10" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136880271</v>
       </c>
       <c r="B13" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136880269</v>
       </c>
       <c r="B14" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37042-2026 artfynd.xlsx
+++ b/artfynd/A 37042-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136880268</v>
       </c>
       <c r="B2" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136877193</v>
       </c>
       <c r="B3" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136880272</v>
       </c>
       <c r="B4" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136880266</v>
       </c>
       <c r="B5" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136880267</v>
       </c>
       <c r="B6" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136933792</v>
       </c>
       <c r="B7" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136880270</v>
       </c>
       <c r="B8" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136933795</v>
       </c>
       <c r="B9" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136933796</v>
       </c>
       <c r="B10" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136933794</v>
       </c>
       <c r="B11" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136880271</v>
       </c>
       <c r="B13" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136880269</v>
       </c>
       <c r="B14" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37042-2026 artfynd.xlsx
+++ b/artfynd/A 37042-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136880268</v>
       </c>
       <c r="B2" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136877193</v>
       </c>
       <c r="B3" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136880272</v>
       </c>
       <c r="B4" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136880266</v>
       </c>
       <c r="B5" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136880267</v>
       </c>
       <c r="B6" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136933792</v>
       </c>
       <c r="B7" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136880270</v>
       </c>
       <c r="B8" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136933795</v>
       </c>
       <c r="B9" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136933796</v>
       </c>
       <c r="B10" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136933794</v>
       </c>
       <c r="B11" t="n">
-        <v>78482</v>
+        <v>78483</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136880271</v>
       </c>
       <c r="B13" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136880269</v>
       </c>
       <c r="B14" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37042-2026 artfynd.xlsx
+++ b/artfynd/A 37042-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136880268</v>
       </c>
       <c r="B2" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136877193</v>
       </c>
       <c r="B3" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136880272</v>
       </c>
       <c r="B4" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37042-2026 artfynd.xlsx
+++ b/artfynd/A 37042-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136880268</v>
       </c>
       <c r="B2" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136877193</v>
       </c>
       <c r="B3" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136880272</v>
       </c>
       <c r="B4" t="n">
-        <v>93448</v>
+        <v>93452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136880266</v>
       </c>
       <c r="B5" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136880267</v>
       </c>
       <c r="B6" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136933792</v>
       </c>
       <c r="B7" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136880270</v>
       </c>
       <c r="B8" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136933795</v>
       </c>
       <c r="B9" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136933796</v>
       </c>
       <c r="B10" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136933794</v>
       </c>
       <c r="B11" t="n">
-        <v>78483</v>
+        <v>78485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136880271</v>
       </c>
       <c r="B13" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136880269</v>
       </c>
       <c r="B14" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37042-2026 artfynd.xlsx
+++ b/artfynd/A 37042-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136880268</v>
       </c>
       <c r="B2" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136877193</v>
       </c>
       <c r="B3" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136880272</v>
       </c>
       <c r="B4" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136880266</v>
       </c>
       <c r="B5" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136880267</v>
       </c>
       <c r="B6" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136933792</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136880270</v>
       </c>
       <c r="B8" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136933795</v>
       </c>
       <c r="B9" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136933796</v>
       </c>
       <c r="B10" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136933794</v>
       </c>
       <c r="B11" t="n">
-        <v>78485</v>
+        <v>78488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136880271</v>
       </c>
       <c r="B13" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136880269</v>
       </c>
       <c r="B14" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37042-2026 artfynd.xlsx
+++ b/artfynd/A 37042-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136880268</v>
       </c>
       <c r="B2" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136877193</v>
       </c>
       <c r="B3" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136880272</v>
       </c>
       <c r="B4" t="n">
-        <v>93454</v>
+        <v>93467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136880266</v>
       </c>
       <c r="B5" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136880267</v>
       </c>
       <c r="B6" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136933792</v>
       </c>
       <c r="B7" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136880270</v>
       </c>
       <c r="B8" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136933795</v>
       </c>
       <c r="B9" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136933796</v>
       </c>
       <c r="B10" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136933794</v>
       </c>
       <c r="B11" t="n">
-        <v>78488</v>
+        <v>78501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136933793</v>
       </c>
       <c r="B12" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136880271</v>
       </c>
       <c r="B13" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136880269</v>
       </c>
       <c r="B14" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37042-2026 artfynd.xlsx
+++ b/artfynd/A 37042-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136880268</v>
       </c>
       <c r="B2" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136877193</v>
       </c>
       <c r="B3" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136880272</v>
       </c>
       <c r="B4" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136880266</v>
       </c>
       <c r="B5" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136880267</v>
       </c>
       <c r="B6" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136933792</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136880270</v>
       </c>
       <c r="B8" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136933795</v>
       </c>
       <c r="B9" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136933796</v>
       </c>
       <c r="B10" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136933794</v>
       </c>
       <c r="B11" t="n">
-        <v>78501</v>
+        <v>78503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136933793</v>
       </c>
       <c r="B12" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136880271</v>
       </c>
       <c r="B13" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136880269</v>
       </c>
       <c r="B14" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37042-2026 artfynd.xlsx
+++ b/artfynd/A 37042-2026 artfynd.xlsx
@@ -1829,11 +1829,7 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Iso Venetvaara, Lu lm</t>

--- a/artfynd/A 37042-2026 artfynd.xlsx
+++ b/artfynd/A 37042-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136880268</v>
       </c>
       <c r="B2" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136877193</v>
       </c>
       <c r="B3" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136880272</v>
       </c>
       <c r="B4" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37042-2026 artfynd.xlsx
+++ b/artfynd/A 37042-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136880268</v>
       </c>
       <c r="B2" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136877193</v>
       </c>
       <c r="B3" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136880272</v>
       </c>
       <c r="B4" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136880266</v>
       </c>
       <c r="B5" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136880267</v>
       </c>
       <c r="B6" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136933792</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136880270</v>
       </c>
       <c r="B8" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136933795</v>
       </c>
       <c r="B9" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136933796</v>
       </c>
       <c r="B10" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136933794</v>
       </c>
       <c r="B11" t="n">
-        <v>78503</v>
+        <v>78513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136933793</v>
       </c>
       <c r="B12" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>136880271</v>
       </c>
       <c r="B13" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136880269</v>
       </c>
       <c r="B14" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37042-2026 artfynd.xlsx
+++ b/artfynd/A 37042-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136880268</v>
       </c>
       <c r="B2" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136877193</v>
       </c>
       <c r="B3" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136880272</v>
       </c>
       <c r="B4" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37042-2026 artfynd.xlsx
+++ b/artfynd/A 37042-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136880268</v>
       </c>
       <c r="B2" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136877193</v>
       </c>
       <c r="B3" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136880272</v>
       </c>
       <c r="B4" t="n">
-        <v>93482</v>
+        <v>93487</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136880266</v>
       </c>
       <c r="B5" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136880267</v>
       </c>
       <c r="B6" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136933792</v>
       </c>
       <c r="B7" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136880270</v>
       </c>
       <c r="B8" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136933795</v>
       </c>
       <c r="B9" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136933796</v>
       </c>
       <c r="B10" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136933794</v>
       </c>
       <c r="B11" t="n">
-        <v>78513</v>
+        <v>78516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136933793</v>
       </c>
       <c r="B12" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>136880271</v>
       </c>
       <c r="B13" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136880269</v>
       </c>
       <c r="B14" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37042-2026 artfynd.xlsx
+++ b/artfynd/A 37042-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136880268</v>
       </c>
       <c r="B2" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136877193</v>
       </c>
       <c r="B3" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136880272</v>
       </c>
       <c r="B4" t="n">
-        <v>93487</v>
+        <v>93489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37042-2026 artfynd.xlsx
+++ b/artfynd/A 37042-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136880268</v>
       </c>
       <c r="B2" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136877193</v>
       </c>
       <c r="B3" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136880272</v>
       </c>
       <c r="B4" t="n">
-        <v>93489</v>
+        <v>93495</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136880266</v>
       </c>
       <c r="B5" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136880267</v>
       </c>
       <c r="B6" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136933792</v>
       </c>
       <c r="B7" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136880270</v>
       </c>
       <c r="B8" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136933795</v>
       </c>
       <c r="B9" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136933796</v>
       </c>
       <c r="B10" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136933794</v>
       </c>
       <c r="B11" t="n">
-        <v>78516</v>
+        <v>78521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136933793</v>
       </c>
       <c r="B12" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>136880271</v>
       </c>
       <c r="B13" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136880269</v>
       </c>
       <c r="B14" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37042-2026 artfynd.xlsx
+++ b/artfynd/A 37042-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136880268</v>
       </c>
       <c r="B2" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136877193</v>
       </c>
       <c r="B3" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136880272</v>
       </c>
       <c r="B4" t="n">
-        <v>93495</v>
+        <v>93507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136880266</v>
       </c>
       <c r="B5" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136880267</v>
       </c>
       <c r="B6" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136933792</v>
       </c>
       <c r="B7" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136880270</v>
       </c>
       <c r="B8" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136933795</v>
       </c>
       <c r="B9" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136933796</v>
       </c>
       <c r="B10" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136933794</v>
       </c>
       <c r="B11" t="n">
-        <v>78521</v>
+        <v>78532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>136880271</v>
       </c>
       <c r="B13" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136880269</v>
       </c>
       <c r="B14" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37042-2026 artfynd.xlsx
+++ b/artfynd/A 37042-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136880268</v>
       </c>
       <c r="B2" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136877193</v>
       </c>
       <c r="B3" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136880272</v>
       </c>
       <c r="B4" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136880266</v>
       </c>
       <c r="B5" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136880267</v>
       </c>
       <c r="B6" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136933792</v>
       </c>
       <c r="B7" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136880270</v>
       </c>
       <c r="B8" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136933795</v>
       </c>
       <c r="B9" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136933796</v>
       </c>
       <c r="B10" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136933794</v>
       </c>
       <c r="B11" t="n">
-        <v>78532</v>
+        <v>78533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>136880271</v>
       </c>
       <c r="B13" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136880269</v>
       </c>
       <c r="B14" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37042-2026 artfynd.xlsx
+++ b/artfynd/A 37042-2026 artfynd.xlsx
@@ -1243,7 +1243,7 @@
         <v>136933792</v>
       </c>
       <c r="B7" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136933795</v>
       </c>
       <c r="B9" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136933796</v>
       </c>
       <c r="B10" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136933794</v>
       </c>
       <c r="B11" t="n">
-        <v>78533</v>
+        <v>78535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37042-2026 artfynd.xlsx
+++ b/artfynd/A 37042-2026 artfynd.xlsx
@@ -1243,7 +1243,7 @@
         <v>136933792</v>
       </c>
       <c r="B7" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136933795</v>
       </c>
       <c r="B9" t="n">
-        <v>78938</v>
+        <v>78939</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136933796</v>
       </c>
       <c r="B10" t="n">
-        <v>80655</v>
+        <v>80656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136933794</v>
       </c>
       <c r="B11" t="n">
-        <v>78535</v>
+        <v>78536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37042-2026 artfynd.xlsx
+++ b/artfynd/A 37042-2026 artfynd.xlsx
@@ -1243,7 +1243,7 @@
         <v>136933792</v>
       </c>
       <c r="B7" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136933795</v>
       </c>
       <c r="B9" t="n">
-        <v>78939</v>
+        <v>78942</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136933796</v>
       </c>
       <c r="B10" t="n">
-        <v>80656</v>
+        <v>80659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136933794</v>
       </c>
       <c r="B11" t="n">
-        <v>78536</v>
+        <v>78539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136933793</v>
       </c>
       <c r="B12" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
